--- a/data/trans_orig/P19C11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue por implantes / solo 2023 en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28893</t>
+          <t>28897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>21250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36901</t>
+          <t>36606</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39485</t>
+          <t>38766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>60859</t>
+          <t>59879</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455548</t>
+          <t>455544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470938</t>
+          <t>470826</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>684715</t>
+          <t>685010</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>700566</t>
+          <t>700366</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1145198</t>
+          <t>1146178</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1166572</t>
+          <t>1167291</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>57683</t>
+          <t>55615</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103726</t>
+          <t>103929</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54573</t>
+          <t>54485</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>94847</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124132</t>
+          <t>124531</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>189615</t>
+          <t>187074</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2126811</t>
+          <t>2126608</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2172854</t>
+          <t>2174922</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2103737</t>
+          <t>2103059</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2143333</t>
+          <t>2143421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4238827</t>
+          <t>4241368</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4304310</t>
+          <t>4303911</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,19%</t>
         </is>
       </c>
     </row>
@@ -1411,17 +1411,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28634</t>
+          <t>28102</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51150</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25116</t>
+          <t>25888</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43031</t>
+          <t>43487</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59427</t>
+          <t>59358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87553</t>
+          <t>88199</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,87%</t>
         </is>
       </c>
     </row>
@@ -1524,17 +1524,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>592308</t>
+          <t>592309</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>580166</t>
+          <t>579959</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>602682</t>
+          <t>603214</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608580</t>
+          <t>608124</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626495</t>
+          <t>625723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1195374</t>
+          <t>1194728</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1223500</t>
+          <t>1223569</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>109835</t>
+          <t>105650</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>168281</t>
+          <t>163669</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111053</t>
+          <t>111952</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160887</t>
+          <t>158272</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>236224</t>
+          <t>240205</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311272</t>
+          <t>312849</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3178012</t>
+          <t>3182624</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3236458</t>
+          <t>3240643</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3410246</t>
+          <t>3412861</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3460080</t>
+          <t>3459181</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,17 +1937,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6639020</t>
+          <t>6639021</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6606154</t>
+          <t>6604578</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6681202</t>
+          <t>6677222</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917426</t>
+          <t>6917427</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P19C11_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19C11_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>20504</t>
+          <t>22898</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28897</t>
+          <t>31909</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>28265</t>
+          <t>30825</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21250</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36606</t>
+          <t>39720</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>48769</t>
+          <t>53722</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38766</t>
+          <t>42529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59879</t>
+          <t>65654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>463937</t>
+          <t>514381</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>455544</t>
+          <t>505370</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>470826</t>
+          <t>521794</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>693351</t>
+          <t>753767</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>685010</t>
+          <t>744872</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>700366</t>
+          <t>761195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1157288</t>
+          <t>1268149</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1146178</t>
+          <t>1256217</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1167291</t>
+          <t>1279342</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,04%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>484441</t>
+          <t>537279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>721616</t>
+          <t>784592</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1206057</t>
+          <t>1321871</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>81163</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55615</t>
+          <t>71803</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>103929</t>
+          <t>111051</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>76000</t>
+          <t>82645</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>54485</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94847</t>
+          <t>98034</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>157163</t>
+          <t>172545</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>124531</t>
+          <t>150493</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>187074</t>
+          <t>198139</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,65%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2149374</t>
+          <t>2056578</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2126608</t>
+          <t>2035427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2174922</t>
+          <t>2074675</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2121906</t>
+          <t>2027947</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2103059</t>
+          <t>2012558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2143421</t>
+          <t>2041719</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4271279</t>
+          <t>4084525</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4241368</t>
+          <t>4058931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4303911</t>
+          <t>4106577</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>96,46%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2230537</t>
+          <t>2146478</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2197906</t>
+          <t>2110592</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4428442</t>
+          <t>4257070</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39007</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28102</t>
+          <t>32248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51357</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33467</t>
+          <t>37344</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>28327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>43487</t>
+          <t>48120</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>72474</t>
+          <t>79809</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59358</t>
+          <t>64245</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88199</t>
+          <t>97467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,83%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>592309</t>
+          <t>659377</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>579959</t>
+          <t>644475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>603214</t>
+          <t>669593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>618144</t>
+          <t>687069</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608124</t>
+          <t>676293</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625723</t>
+          <t>696086</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1210453</t>
+          <t>1346445</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1194728</t>
+          <t>1328787</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1223569</t>
+          <t>1362009</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>94,35%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,13%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,5%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>631316</t>
+          <t>701841</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651611</t>
+          <t>724413</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1282927</t>
+          <t>1426254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>140674</t>
+          <t>155262</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>105650</t>
+          <t>129219</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>163669</t>
+          <t>179618</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>137732</t>
+          <t>150814</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>111952</t>
+          <t>133450</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158272</t>
+          <t>172604</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>278406</t>
+          <t>306076</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>240205</t>
+          <t>275551</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312849</t>
+          <t>339658</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3205619</t>
+          <t>3230336</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3182624</t>
+          <t>3205980</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3240643</t>
+          <t>3256379</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3433401</t>
+          <t>3468783</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3412861</t>
+          <t>3446993</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3459181</t>
+          <t>3486147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6639021</t>
+          <t>6699119</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6604578</t>
+          <t>6665537</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6677222</t>
+          <t>6729644</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3346293</t>
+          <t>3385598</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3571133</t>
+          <t>3619597</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6917427</t>
+          <t>7005195</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
